--- a/EndResult/100m Rygg.xlsx
+++ b/EndResult/100m Rygg.xlsx
@@ -1278,20 +1278,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.02,79</t>
+          <t>1.00,47</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>668</v>
+        <v>712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16.11.2024</t>
+          <t>15.11.2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bodø</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/EndResult/100m Rygg.xlsx
+++ b/EndResult/100m Rygg.xlsx
@@ -476,20 +476,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58,48</t>
+          <t>58,35</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>03.12.2024</t>
+          <t>13.06.2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -681,20 +681,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Albert Barrabino</t>
+          <t>Balder Baarholm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.01,93</t>
+          <t>1.01,78</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>06.10.2012</t>
+          <t>24.01.2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -716,20 +716,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Thomas Trøite</t>
+          <t>Albert Barrabino</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.01,95</t>
+          <t>1.01,93</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>06.10.2012</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -751,12 +751,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sebastian Amundsen</t>
+          <t>Thomas Trøite</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.01,97</t>
+          <t>1.01,95</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -764,12 +764,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>02.11.2019</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -786,20 +786,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Erlend Tofte Haarsaker</t>
+          <t>Sebastian Amundsen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.02,28</t>
+          <t>1.01,97</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>17.03.2013</t>
+          <t>02.11.2019</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -877,20 +877,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.00,67</t>
+          <t>1.00,52</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>07.07.2024</t>
+          <t>09.05.2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1012,7 +1012,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Eirik Hakvåg-Sandengen</t>
+          <t>Balder Baarholm</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1025,12 +1025,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>27.06.2025</t>
+          <t>18.04.2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1047,20 +1047,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Simon Moe</t>
+          <t>Eirik Hakvåg-Sandengen</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.06,25</t>
+          <t>1.06,07</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>01.07.2016</t>
+          <t>27.06.2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1082,25 +1082,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bergman Olof Andreas</t>
+          <t>Simon Moe</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.06,65</t>
+          <t>1.06,25</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>09.06.2018</t>
+          <t>01.07.2016</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gleb Eriksson</t>
+          <t>Bergman Olof Andreas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10.07.2005</t>
+          <t>09.06.2018</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1152,25 +1152,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Manith Randula Attanapola</t>
+          <t>Gleb Eriksson</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.06,87</t>
+          <t>1.06,65</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>07.07.2015</t>
+          <t>10.07.2005</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1187,25 +1187,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kristian Volden</t>
+          <t>Mattias Isaksen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.06,89</t>
+          <t>1.06,82</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>06.03.2016</t>
+          <t>19.04.2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1278,20 +1278,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.00,47</t>
+          <t>1.00,88</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>712</v>
+        <v>732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>15.11.2025</t>
+          <t>25.01.2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1518,12 +1518,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Renate Knutsen</t>
+          <t>Mia Olden Larsen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.09,32</t>
+          <t>1.09,33</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>14.01.2023</t>
+          <t>18.10.2014</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1553,12 +1553,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mia Olden Larsen</t>
+          <t>Renate Knutsen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.09,33</t>
+          <t>1.09,32</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18.10.2014</t>
+          <t>14.01.2023</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1679,20 +1679,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.04,29</t>
+          <t>1.02,87</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>709</v>
+        <v>758</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>04.07.2025</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rud</t>
+          <t>Tøyen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
